--- a/Excel Lec/Lookups/day 2.xlsx
+++ b/Excel Lec/Lookups/day 2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Programming\DA pyth [Anudip]\Excel Lec\Lookups\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\navne\OneDrive - GN Group Of Institutes\Desktop\Anudip github\Anudip-LA\Excel Lec\Lookups\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87EE3623-AC08-4C22-9B31-6731C95F917C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C9BF174-08FC-4ABD-A7D5-FC90A26A8455}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VLOOKUP" sheetId="1" r:id="rId1"/>
@@ -363,8 +363,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -443,13 +443,13 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
